--- a/list_federal_judges_party.xlsx
+++ b/list_federal_judges_party.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\misch\project3-bundesgericht\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91388054-5E64-442B-9275-D9CF914EFC09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94B42D26-CABC-495C-95DA-4DF9C1D0AB03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1049,7 +1049,7 @@
         <v>190</v>
       </c>
       <c r="I2" t="str">
-        <f>IF(OR(G2="CVP",27="Die Mitte"),"Mitte",G2)</f>
+        <f>IF(OR(G2="CVP",27="Die Mitte"),"Die Mitte",G2)</f>
         <v>SVP</v>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
         <v>41</v>
       </c>
       <c r="I3" t="str">
-        <f>IF(OR(G3="CVP",27="Die Mitte"),"Mitte",G3)</f>
+        <f t="shared" ref="I3:I61" si="0">IF(OR(G3="CVP",27="Die Mitte"),"Die Mitte",G3)</f>
         <v>SP</v>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
         <v>45</v>
       </c>
       <c r="I4" t="str">
-        <f t="shared" ref="I4:I27" si="0">IF(OR(G4="CVP",27="Die Mitte"),"Mitte",G4)</f>
+        <f t="shared" si="0"/>
         <v>Grüne</v>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="I12" t="str">
         <f t="shared" si="0"/>
-        <v>Mitte</v>
+        <v>Die Mitte</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
@@ -1694,7 +1694,7 @@
         <v>109</v>
       </c>
       <c r="I28" t="str">
-        <f>IF(OR(G28="CVP",27="Die Mitte"),"Mitte",G28)</f>
+        <f t="shared" si="0"/>
         <v>SVP</v>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
         <v>111</v>
       </c>
       <c r="I29" t="str">
-        <f>IF(OR(G28="CVP",G28="Die Mitte"),"Mitte",G29)</f>
+        <f t="shared" si="0"/>
         <v>SVP</v>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
         <v>113</v>
       </c>
       <c r="I30" t="str">
-        <f t="shared" ref="I30:I61" si="1">IF(OR(G29="CVP",G29="Die Mitte"),"Mitte",G30)</f>
+        <f t="shared" si="0"/>
         <v>SVP</v>
       </c>
     </row>
@@ -1772,7 +1772,7 @@
         <v>116</v>
       </c>
       <c r="I31" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>FDP</v>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
         <v>118</v>
       </c>
       <c r="I32" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>SP</v>
       </c>
     </row>
@@ -1820,8 +1820,8 @@
         <v>120</v>
       </c>
       <c r="I33" t="str">
-        <f>IF(OR(G33="CVP",G32="Die Mitte"),"Mitte",G32)</f>
-        <v>SP</v>
+        <f t="shared" si="0"/>
+        <v>SVP</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
@@ -1844,7 +1844,7 @@
         <v>123</v>
       </c>
       <c r="I34" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Grüne</v>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
         <v>125</v>
       </c>
       <c r="I35" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>FDP</v>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
         <v>127</v>
       </c>
       <c r="I36" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Die Mitte</v>
       </c>
     </row>
@@ -1919,8 +1919,8 @@
         <v>129</v>
       </c>
       <c r="I37" t="str">
-        <f t="shared" si="1"/>
-        <v>Mitte</v>
+        <f t="shared" si="0"/>
+        <v>FDP</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
@@ -1946,7 +1946,7 @@
         <v>131</v>
       </c>
       <c r="I38" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>SVP</v>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
         <v>133</v>
       </c>
       <c r="I39" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Die Mitte</v>
       </c>
     </row>
@@ -1994,8 +1994,8 @@
         <v>135</v>
       </c>
       <c r="I40" t="str">
-        <f t="shared" si="1"/>
-        <v>Mitte</v>
+        <f t="shared" si="0"/>
+        <v>Grüne</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
@@ -2018,7 +2018,7 @@
         <v>137</v>
       </c>
       <c r="I41" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Grüne</v>
       </c>
     </row>
@@ -2042,7 +2042,7 @@
         <v>140</v>
       </c>
       <c r="I42" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>SVP</v>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
         <v>142</v>
       </c>
       <c r="I43" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>SVP</v>
       </c>
     </row>
@@ -2090,7 +2090,7 @@
         <v>144</v>
       </c>
       <c r="I44" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>FDP</v>
       </c>
     </row>
@@ -2117,8 +2117,8 @@
         <v>147</v>
       </c>
       <c r="I45" t="str">
-        <f t="shared" si="1"/>
-        <v>CVP</v>
+        <f t="shared" si="0"/>
+        <v>Die Mitte</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.35">
@@ -2144,8 +2144,8 @@
         <v>150</v>
       </c>
       <c r="I46" t="str">
-        <f t="shared" si="1"/>
-        <v>Mitte</v>
+        <f t="shared" si="0"/>
+        <v>SP</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
@@ -2168,7 +2168,7 @@
         <v>152</v>
       </c>
       <c r="I47" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>SP</v>
       </c>
     </row>
@@ -2195,7 +2195,7 @@
         <v>154</v>
       </c>
       <c r="I48" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Grüne</v>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
         <v>157</v>
       </c>
       <c r="I49" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>SVP</v>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
         <v>159</v>
       </c>
       <c r="I50" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>SP</v>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
         <v>162</v>
       </c>
       <c r="I51" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>FDP</v>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
         <v>165</v>
       </c>
       <c r="I52" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>BDP</v>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
         <v>168</v>
       </c>
       <c r="I53" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Die Mitte</v>
       </c>
     </row>
@@ -2345,8 +2345,8 @@
         <v>170</v>
       </c>
       <c r="I54" t="str">
-        <f t="shared" si="1"/>
-        <v>Mitte</v>
+        <f t="shared" si="0"/>
+        <v>SVP</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.35">
@@ -2369,7 +2369,7 @@
         <v>173</v>
       </c>
       <c r="I55" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>SVP</v>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
         <v>176</v>
       </c>
       <c r="I56" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>SVP</v>
       </c>
     </row>
@@ -2417,7 +2417,7 @@
         <v>179</v>
       </c>
       <c r="I57" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>Die Mitte</v>
       </c>
     </row>
@@ -2444,8 +2444,8 @@
         <v>181</v>
       </c>
       <c r="I58" t="str">
-        <f t="shared" si="1"/>
-        <v>Mitte</v>
+        <f t="shared" si="0"/>
+        <v>SVP</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.35">
@@ -2471,7 +2471,7 @@
         <v>183</v>
       </c>
       <c r="I59" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>SP</v>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
         <v>185</v>
       </c>
       <c r="I60" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>SP</v>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
         <v>187</v>
       </c>
       <c r="I61" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>SP</v>
       </c>
     </row>

--- a/list_federal_judges_party.xlsx
+++ b/list_federal_judges_party.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\misch\project3-bundesgericht\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94B42D26-CABC-495C-95DA-4DF9C1D0AB03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2902BC60-F048-4909-864D-9AF36C009FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="206">
   <si>
     <t>SP</t>
   </si>
@@ -147,9 +147,6 @@
   </si>
   <si>
     <t>Marti-Schreier</t>
-  </si>
-  <si>
-    <t>Mitte</t>
   </si>
   <si>
     <t>Bernard Abrecht</t>
@@ -1008,36 +1005,36 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E1" t="s">
+        <v>205</v>
+      </c>
+      <c r="F1" t="s">
+        <v>203</v>
+      </c>
+      <c r="G1" t="s">
+        <v>200</v>
+      </c>
+      <c r="H1" t="s">
         <v>202</v>
       </c>
-      <c r="B1" t="s">
-        <v>199</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D1" t="s">
-        <v>200</v>
-      </c>
-      <c r="E1" t="s">
-        <v>206</v>
-      </c>
-      <c r="F1" t="s">
-        <v>204</v>
-      </c>
-      <c r="G1" t="s">
-        <v>201</v>
-      </c>
-      <c r="H1" t="s">
-        <v>203</v>
-      </c>
       <c r="I1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B2">
         <v>2026</v>
@@ -1046,7 +1043,7 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I2" t="str">
         <f>IF(OR(G2="CVP",27="Die Mitte"),"Die Mitte",G2)</f>
@@ -1055,7 +1052,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3">
         <v>2019</v>
@@ -1064,13 +1061,13 @@
         <v>1966</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G3" t="s">
         <v>0</v>
       </c>
       <c r="H3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I3" t="str">
         <f t="shared" ref="I3:I61" si="0">IF(OR(G3="CVP",27="Die Mitte"),"Die Mitte",G3)</f>
@@ -1079,7 +1076,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4">
         <v>2007</v>
@@ -1088,13 +1085,13 @@
         <v>1964</v>
       </c>
       <c r="F4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G4" t="s">
         <v>43</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>44</v>
-      </c>
-      <c r="H4" t="s">
-        <v>45</v>
       </c>
       <c r="I4" t="str">
         <f t="shared" si="0"/>
@@ -1103,7 +1100,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B5">
         <v>2019</v>
@@ -1112,13 +1109,13 @@
         <v>1969</v>
       </c>
       <c r="F5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G5" t="s">
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I5" t="str">
         <f t="shared" si="0"/>
@@ -1127,7 +1124,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B6">
         <v>2024</v>
@@ -1136,13 +1133,13 @@
         <v>1974</v>
       </c>
       <c r="F6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G6" t="s">
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I6" t="str">
         <f t="shared" si="0"/>
@@ -1151,7 +1148,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B7">
         <v>2014</v>
@@ -1160,13 +1157,13 @@
         <v>1973</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G7" t="s">
         <v>2</v>
       </c>
       <c r="H7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I7" t="str">
         <f t="shared" si="0"/>
@@ -1175,7 +1172,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B8">
         <v>2011</v>
@@ -1184,13 +1181,13 @@
         <v>1964</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G8" t="s">
         <v>2</v>
       </c>
       <c r="H8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I8" t="str">
         <f t="shared" si="0"/>
@@ -1199,7 +1196,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B9">
         <v>2011</v>
@@ -1208,13 +1205,13 @@
         <v>1967</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I9" t="str">
         <f t="shared" si="0"/>
@@ -1223,7 +1220,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B10">
         <v>2022</v>
@@ -1232,13 +1229,13 @@
         <v>1974</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G10" t="s">
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I10" t="str">
         <f t="shared" si="0"/>
@@ -1247,7 +1244,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B11">
         <v>2008</v>
@@ -1256,13 +1253,13 @@
         <v>1961</v>
       </c>
       <c r="F11" t="s">
+        <v>63</v>
+      </c>
+      <c r="G11" t="s">
         <v>64</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>65</v>
-      </c>
-      <c r="H11" t="s">
-        <v>66</v>
       </c>
       <c r="I11" t="str">
         <f t="shared" si="0"/>
@@ -1271,7 +1268,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B12">
         <v>2004</v>
@@ -1283,13 +1280,13 @@
         <v>1950</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G12" t="s">
+        <v>67</v>
+      </c>
+      <c r="H12" t="s">
         <v>68</v>
-      </c>
-      <c r="H12" t="s">
-        <v>69</v>
       </c>
       <c r="I12" t="str">
         <f t="shared" si="0"/>
@@ -1298,7 +1295,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B13">
         <v>2002</v>
@@ -1310,13 +1307,13 @@
         <v>1957</v>
       </c>
       <c r="F13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G13" t="s">
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I13" t="str">
         <f t="shared" si="0"/>
@@ -1325,7 +1322,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B14">
         <v>2002</v>
@@ -1337,13 +1334,13 @@
         <v>1953</v>
       </c>
       <c r="F14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G14" t="s">
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I14" t="str">
         <f t="shared" si="0"/>
@@ -1352,7 +1349,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B15">
         <v>2011</v>
@@ -1367,13 +1364,13 @@
         <v>2022</v>
       </c>
       <c r="F15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G15" t="s">
         <v>2</v>
       </c>
       <c r="H15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I15" t="str">
         <f t="shared" si="0"/>
@@ -1382,7 +1379,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B16">
         <v>2025</v>
@@ -1391,13 +1388,13 @@
         <v>1977</v>
       </c>
       <c r="F16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" t="s">
         <v>78</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>79</v>
-      </c>
-      <c r="H16" t="s">
-        <v>80</v>
       </c>
       <c r="I16" t="str">
         <f t="shared" si="0"/>
@@ -1406,7 +1403,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B17">
         <v>2024</v>
@@ -1415,13 +1412,13 @@
         <v>1976</v>
       </c>
       <c r="F17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G17" t="s">
         <v>1</v>
       </c>
       <c r="H17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I17" t="str">
         <f t="shared" si="0"/>
@@ -1430,7 +1427,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B18">
         <v>2014</v>
@@ -1439,13 +1436,13 @@
         <v>1960</v>
       </c>
       <c r="F18" t="s">
+        <v>83</v>
+      </c>
+      <c r="G18" t="s">
         <v>84</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>85</v>
-      </c>
-      <c r="H18" t="s">
-        <v>86</v>
       </c>
       <c r="I18" t="str">
         <f t="shared" si="0"/>
@@ -1454,7 +1451,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B19">
         <v>2019</v>
@@ -1463,10 +1460,10 @@
         <v>1977</v>
       </c>
       <c r="F19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H19" t="s">
         <v>3</v>
@@ -1478,7 +1475,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B20">
         <v>2021</v>
@@ -1487,13 +1484,13 @@
         <v>1972</v>
       </c>
       <c r="F20" t="s">
+        <v>89</v>
+      </c>
+      <c r="G20" t="s">
+        <v>43</v>
+      </c>
+      <c r="H20" t="s">
         <v>90</v>
-      </c>
-      <c r="G20" t="s">
-        <v>44</v>
-      </c>
-      <c r="H20" t="s">
-        <v>91</v>
       </c>
       <c r="I20" t="str">
         <f t="shared" si="0"/>
@@ -1502,7 +1499,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B21">
         <v>2012</v>
@@ -1511,13 +1508,13 @@
         <v>1969</v>
       </c>
       <c r="F21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G21" t="s">
         <v>1</v>
       </c>
       <c r="H21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I21" t="str">
         <f t="shared" si="0"/>
@@ -1526,7 +1523,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B22">
         <v>2009</v>
@@ -1535,13 +1532,13 @@
         <v>1961</v>
       </c>
       <c r="F22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G22" t="s">
         <v>1</v>
       </c>
       <c r="H22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I22" t="str">
         <f t="shared" si="0"/>
@@ -1550,7 +1547,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B23">
         <v>2002</v>
@@ -1562,13 +1559,13 @@
         <v>1956</v>
       </c>
       <c r="F23" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G23" t="s">
         <v>2</v>
       </c>
       <c r="H23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I23" t="str">
         <f t="shared" si="0"/>
@@ -1577,7 +1574,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B24">
         <v>2023</v>
@@ -1586,13 +1583,13 @@
         <v>1978</v>
       </c>
       <c r="F24" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H24" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I24" t="str">
         <f t="shared" si="0"/>
@@ -1601,7 +1598,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B25">
         <v>2020</v>
@@ -1610,13 +1607,13 @@
         <v>1979</v>
       </c>
       <c r="F25" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G25" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I25" t="str">
         <f t="shared" si="0"/>
@@ -1625,7 +1622,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B26">
         <v>2007</v>
@@ -1634,13 +1631,13 @@
         <v>1957</v>
       </c>
       <c r="F26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H26" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I26" t="str">
         <f t="shared" si="0"/>
@@ -1649,7 +1646,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B27">
         <v>2015</v>
@@ -1661,13 +1658,13 @@
         <v>1956</v>
       </c>
       <c r="F27" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G27" t="s">
         <v>1</v>
       </c>
       <c r="H27" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I27" t="str">
         <f t="shared" si="0"/>
@@ -1676,7 +1673,7 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B28">
         <v>2024</v>
@@ -1685,13 +1682,13 @@
         <v>1973</v>
       </c>
       <c r="F28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G28" t="s">
         <v>1</v>
       </c>
       <c r="H28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I28" t="str">
         <f t="shared" si="0"/>
@@ -1700,7 +1697,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B29">
         <v>2001</v>
@@ -1712,13 +1709,13 @@
         <v>1958</v>
       </c>
       <c r="F29" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G29" t="s">
         <v>1</v>
       </c>
       <c r="H29" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I29" t="str">
         <f t="shared" si="0"/>
@@ -1727,7 +1724,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B30">
         <v>2001</v>
@@ -1739,13 +1736,13 @@
         <v>1955</v>
       </c>
       <c r="F30" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G30" t="s">
         <v>1</v>
       </c>
       <c r="H30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I30" t="str">
         <f t="shared" si="0"/>
@@ -1754,7 +1751,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B31">
         <v>2003</v>
@@ -1763,13 +1760,13 @@
         <v>1960</v>
       </c>
       <c r="F31" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G31" t="s">
         <v>2</v>
       </c>
       <c r="H31" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I31" t="str">
         <f t="shared" si="0"/>
@@ -1778,7 +1775,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B32">
         <v>2012</v>
@@ -1787,13 +1784,13 @@
         <v>1965</v>
       </c>
       <c r="F32" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G32" t="s">
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I32" t="str">
         <f t="shared" si="0"/>
@@ -1802,7 +1799,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B33">
         <v>2019</v>
@@ -1811,13 +1808,13 @@
         <v>1976</v>
       </c>
       <c r="F33" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G33" t="s">
         <v>1</v>
       </c>
       <c r="H33" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I33" t="str">
         <f t="shared" si="0"/>
@@ -1826,7 +1823,7 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B34">
         <v>2022</v>
@@ -1835,13 +1832,13 @@
         <v>1980</v>
       </c>
       <c r="F34" t="s">
+        <v>121</v>
+      </c>
+      <c r="G34" t="s">
+        <v>43</v>
+      </c>
+      <c r="H34" t="s">
         <v>122</v>
-      </c>
-      <c r="G34" t="s">
-        <v>44</v>
-      </c>
-      <c r="H34" t="s">
-        <v>123</v>
       </c>
       <c r="I34" t="str">
         <f t="shared" si="0"/>
@@ -1850,7 +1847,7 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B35">
         <v>2023</v>
@@ -1859,13 +1856,13 @@
         <v>1985</v>
       </c>
       <c r="F35" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G35" t="s">
         <v>2</v>
       </c>
       <c r="H35" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I35" t="str">
         <f t="shared" si="0"/>
@@ -1874,7 +1871,7 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B36">
         <v>2008</v>
@@ -1883,13 +1880,13 @@
         <v>1959</v>
       </c>
       <c r="F36" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G36" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H36" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I36" t="str">
         <f t="shared" si="0"/>
@@ -1898,7 +1895,7 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B37">
         <v>2002</v>
@@ -1910,13 +1907,13 @@
         <v>1955</v>
       </c>
       <c r="F37" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G37" t="s">
         <v>2</v>
       </c>
       <c r="H37" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I37" t="str">
         <f t="shared" si="0"/>
@@ -1925,7 +1922,7 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B38">
         <v>2006</v>
@@ -1937,13 +1934,13 @@
         <v>1946</v>
       </c>
       <c r="F38" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G38" t="s">
         <v>1</v>
       </c>
       <c r="H38" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I38" t="str">
         <f t="shared" si="0"/>
@@ -1952,7 +1949,7 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B39">
         <v>2016</v>
@@ -1961,13 +1958,13 @@
         <v>1973</v>
       </c>
       <c r="F39" t="s">
+        <v>77</v>
+      </c>
+      <c r="G39" t="s">
         <v>78</v>
       </c>
-      <c r="G39" t="s">
-        <v>79</v>
-      </c>
       <c r="H39" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I39" t="str">
         <f t="shared" si="0"/>
@@ -1976,7 +1973,7 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B40">
         <v>2020</v>
@@ -1985,13 +1982,13 @@
         <v>1964</v>
       </c>
       <c r="F40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H40" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I40" t="str">
         <f t="shared" si="0"/>
@@ -2000,7 +1997,7 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B41">
         <v>2023</v>
@@ -2009,13 +2006,13 @@
         <v>1973</v>
       </c>
       <c r="F41" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G41" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H41" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I41" t="str">
         <f t="shared" si="0"/>
@@ -2024,7 +2021,7 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B42">
         <v>2014</v>
@@ -2033,13 +2030,13 @@
         <v>1971</v>
       </c>
       <c r="F42" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G42" t="s">
         <v>1</v>
       </c>
       <c r="H42" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I42" t="str">
         <f t="shared" si="0"/>
@@ -2048,7 +2045,7 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B43">
         <v>2019</v>
@@ -2057,13 +2054,13 @@
         <v>1964</v>
       </c>
       <c r="F43" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G43" t="s">
         <v>1</v>
       </c>
       <c r="H43" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I43" t="str">
         <f t="shared" si="0"/>
@@ -2072,7 +2069,7 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B44">
         <v>2018</v>
@@ -2081,13 +2078,13 @@
         <v>1964</v>
       </c>
       <c r="F44" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G44" t="s">
         <v>2</v>
       </c>
       <c r="H44" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I44" t="str">
         <f t="shared" si="0"/>
@@ -2096,7 +2093,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B45">
         <v>2009</v>
@@ -2108,13 +2105,13 @@
         <v>1954</v>
       </c>
       <c r="F45" t="s">
+        <v>145</v>
+      </c>
+      <c r="G45" t="s">
+        <v>67</v>
+      </c>
+      <c r="H45" t="s">
         <v>146</v>
-      </c>
-      <c r="G45" t="s">
-        <v>68</v>
-      </c>
-      <c r="H45" t="s">
-        <v>147</v>
       </c>
       <c r="I45" t="str">
         <f t="shared" si="0"/>
@@ -2123,7 +2120,7 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B46">
         <v>2013</v>
@@ -2135,13 +2132,13 @@
         <v>1953</v>
       </c>
       <c r="F46" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G46" t="s">
         <v>0</v>
       </c>
       <c r="H46" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I46" t="str">
         <f t="shared" si="0"/>
@@ -2150,7 +2147,7 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B47">
         <v>2013</v>
@@ -2159,13 +2156,13 @@
         <v>1967</v>
       </c>
       <c r="F47" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G47" t="s">
         <v>0</v>
       </c>
       <c r="H47" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I47" t="str">
         <f t="shared" si="0"/>
@@ -2174,7 +2171,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B48">
         <v>2009</v>
@@ -2186,13 +2183,13 @@
         <v>1951</v>
       </c>
       <c r="F48" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G48" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H48" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I48" t="str">
         <f t="shared" si="0"/>
@@ -2201,7 +2198,7 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B49">
         <v>2013</v>
@@ -2210,13 +2207,13 @@
         <v>1976</v>
       </c>
       <c r="F49" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G49" t="s">
         <v>1</v>
       </c>
       <c r="H49" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I49" t="str">
         <f t="shared" si="0"/>
@@ -2225,7 +2222,7 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B50">
         <v>2021</v>
@@ -2234,13 +2231,13 @@
         <v>1968</v>
       </c>
       <c r="F50" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G50" t="s">
         <v>0</v>
       </c>
       <c r="H50" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I50" t="str">
         <f t="shared" si="0"/>
@@ -2249,7 +2246,7 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B51">
         <v>2022</v>
@@ -2258,13 +2255,13 @@
         <v>1970</v>
       </c>
       <c r="F51" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G51" t="s">
         <v>2</v>
       </c>
       <c r="H51" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I51" t="str">
         <f t="shared" si="0"/>
@@ -2273,7 +2270,7 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B52">
         <v>2012</v>
@@ -2285,13 +2282,13 @@
         <v>1958</v>
       </c>
       <c r="F52" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G52" t="s">
+        <v>163</v>
+      </c>
+      <c r="H52" t="s">
         <v>164</v>
-      </c>
-      <c r="H52" t="s">
-        <v>165</v>
       </c>
       <c r="I52" t="str">
         <f t="shared" si="0"/>
@@ -2300,7 +2297,7 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B53">
         <v>2009</v>
@@ -2309,13 +2306,13 @@
         <v>1958</v>
       </c>
       <c r="F53" t="s">
+        <v>166</v>
+      </c>
+      <c r="G53" t="s">
+        <v>78</v>
+      </c>
+      <c r="H53" t="s">
         <v>167</v>
-      </c>
-      <c r="G53" t="s">
-        <v>79</v>
-      </c>
-      <c r="H53" t="s">
-        <v>168</v>
       </c>
       <c r="I53" t="str">
         <f t="shared" si="0"/>
@@ -2324,7 +2321,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B54">
         <v>2001</v>
@@ -2336,13 +2333,13 @@
         <v>1953</v>
       </c>
       <c r="F54" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G54" t="s">
         <v>1</v>
       </c>
       <c r="H54" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I54" t="str">
         <f t="shared" si="0"/>
@@ -2351,7 +2348,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B55">
         <v>2019</v>
@@ -2360,13 +2357,13 @@
         <v>1971</v>
       </c>
       <c r="F55" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G55" t="s">
         <v>1</v>
       </c>
       <c r="H55" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I55" t="str">
         <f t="shared" si="0"/>
@@ -2375,7 +2372,7 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B56">
         <v>2016</v>
@@ -2384,13 +2381,13 @@
         <v>1963</v>
       </c>
       <c r="F56" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G56" t="s">
         <v>1</v>
       </c>
       <c r="H56" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I56" t="str">
         <f t="shared" si="0"/>
@@ -2399,7 +2396,7 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B57">
         <v>2023</v>
@@ -2408,13 +2405,13 @@
         <v>1971</v>
       </c>
       <c r="F57" t="s">
+        <v>177</v>
+      </c>
+      <c r="G57" t="s">
+        <v>78</v>
+      </c>
+      <c r="H57" t="s">
         <v>178</v>
-      </c>
-      <c r="G57" t="s">
-        <v>79</v>
-      </c>
-      <c r="H57" t="s">
-        <v>179</v>
       </c>
       <c r="I57" t="str">
         <f t="shared" si="0"/>
@@ -2423,7 +2420,7 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B58">
         <v>2009</v>
@@ -2435,13 +2432,13 @@
         <v>1959</v>
       </c>
       <c r="F58" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G58" t="s">
         <v>1</v>
       </c>
       <c r="H58" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I58" t="str">
         <f t="shared" si="0"/>
@@ -2450,7 +2447,7 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B59">
         <v>2016</v>
@@ -2462,13 +2459,13 @@
         <v>1959</v>
       </c>
       <c r="F59" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G59" t="s">
         <v>0</v>
       </c>
       <c r="H59" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I59" t="str">
         <f t="shared" si="0"/>
@@ -2477,7 +2474,7 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B60">
         <v>2024</v>
@@ -2486,13 +2483,13 @@
         <v>1975</v>
       </c>
       <c r="F60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G60" t="s">
         <v>0</v>
       </c>
       <c r="H60" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I60" t="str">
         <f t="shared" si="0"/>
@@ -2501,7 +2498,7 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B61">
         <v>2004</v>
@@ -2513,13 +2510,13 @@
         <v>1957</v>
       </c>
       <c r="F61" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G61" t="s">
         <v>0</v>
       </c>
       <c r="H61" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I61" t="str">
         <f t="shared" si="0"/>
@@ -2575,7 +2572,7 @@
         <v>8</v>
       </c>
       <c r="H66" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I66" t="s">
         <v>0</v>
@@ -2586,7 +2583,7 @@
         <v>25</v>
       </c>
       <c r="H67" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I67" t="s">
         <v>2</v>
@@ -2644,7 +2641,7 @@
         <v>30</v>
       </c>
       <c r="I72" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.35">
@@ -2666,7 +2663,7 @@
         <v>32</v>
       </c>
       <c r="I74" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.35">
@@ -2726,21 +2723,21 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
+        <v>191</v>
+      </c>
+      <c r="H80" t="s">
         <v>192</v>
       </c>
-      <c r="H80" t="s">
-        <v>193</v>
-      </c>
       <c r="I80" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H81" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I81" t="s">
         <v>1</v>
@@ -2748,10 +2745,10 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
+        <v>195</v>
+      </c>
+      <c r="H82" t="s">
         <v>196</v>
-      </c>
-      <c r="H82" t="s">
-        <v>197</v>
       </c>
       <c r="I82" t="s">
         <v>0</v>
